--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -136,7 +136,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>DOU + Djinni — Product Design / UI/UX вакансії</a:t>
+              <a:t>DOU + Djinni — кількість вакансій на борді</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>76</v>
+        <v>244</v>
       </c>
       <c r="C2" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -168,12 +168,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2</f>
+              <f>'Counts'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$B$2</f>
+              <f>'Counts'!$B$2:$B$3</f>
             </numRef>
           </val>
         </ser>
@@ -200,12 +200,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2</f>
+              <f>'Counts'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$C$2</f>
+              <f>'Counts'!$C$2:$C$3</f>
             </numRef>
           </val>
         </ser>
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -613,13 +613,26 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>254</v>
+      </c>
+      <c r="C2" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B3" t="n">
         <v>244</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C3" t="n">
         <v>78</v>
       </c>
     </row>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C3" t="n">
         <v>78</v>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -168,12 +168,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$3</f>
+              <f>'Counts'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$B$2:$B$3</f>
+              <f>'Counts'!$B$2:$B$4</f>
             </numRef>
           </val>
         </ser>
@@ -200,12 +200,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Counts'!$A$2:$A$3</f>
+              <f>'Counts'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Counts'!$C$2:$C$3</f>
+              <f>'Counts'!$C$2:$C$4</f>
             </numRef>
           </val>
         </ser>
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -636,6 +636,19 @@
         <v>78</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>232</v>
+      </c>
+      <c r="C4" t="n">
+        <v>77</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/reports/vacancy-analytics.xlsx
+++ b/reports/vacancy-analytics.xlsx
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C4" t="n">
         <v>77</v>
